--- a/dist/data/02_Matrice_Optional_Ferretti.xlsx
+++ b/dist/data/02_Matrice_Optional_Ferretti.xlsx
@@ -2464,130 +2464,378 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
-      <c r="BW4" t="inlineStr"/>
-      <c r="BX4" t="inlineStr"/>
-      <c r="BY4" t="inlineStr"/>
-      <c r="BZ4" t="inlineStr"/>
-      <c r="CA4" t="inlineStr"/>
-      <c r="CB4" t="inlineStr"/>
-      <c r="CC4" t="inlineStr"/>
-      <c r="CD4" t="inlineStr"/>
-      <c r="CE4" t="inlineStr"/>
-      <c r="CF4" t="inlineStr"/>
-      <c r="CG4" t="inlineStr"/>
-      <c r="CH4" t="inlineStr"/>
-      <c r="CI4" t="inlineStr"/>
-      <c r="CJ4" t="inlineStr"/>
-      <c r="CK4" t="inlineStr"/>
-      <c r="CL4" t="inlineStr"/>
-      <c r="CM4" t="inlineStr"/>
-      <c r="CN4" t="inlineStr"/>
-      <c r="CO4" t="inlineStr"/>
-      <c r="CP4" t="inlineStr"/>
-      <c r="CQ4" t="inlineStr"/>
-      <c r="CR4" t="inlineStr"/>
-      <c r="CS4" t="inlineStr"/>
-      <c r="CT4" t="inlineStr"/>
-      <c r="CU4" t="inlineStr"/>
-      <c r="CV4" t="inlineStr"/>
-      <c r="CW4" t="inlineStr"/>
-      <c r="CX4" t="inlineStr"/>
-      <c r="CY4" t="inlineStr"/>
-      <c r="CZ4" t="inlineStr"/>
-      <c r="DA4" t="inlineStr"/>
-      <c r="DB4" t="inlineStr"/>
-      <c r="DC4" t="inlineStr"/>
-      <c r="DD4" t="inlineStr"/>
-      <c r="DE4" t="inlineStr"/>
-      <c r="DF4" t="inlineStr"/>
-      <c r="DG4" t="inlineStr"/>
-      <c r="DH4" t="inlineStr"/>
-      <c r="DI4" t="inlineStr"/>
-      <c r="DJ4" t="inlineStr"/>
-      <c r="DK4" t="inlineStr"/>
-      <c r="DL4" t="inlineStr"/>
-      <c r="DM4" t="inlineStr"/>
-      <c r="DN4" t="inlineStr"/>
-      <c r="DO4" t="inlineStr"/>
-      <c r="DP4" t="inlineStr"/>
-      <c r="DQ4" t="inlineStr"/>
-      <c r="DR4" t="inlineStr"/>
-      <c r="DS4" t="inlineStr"/>
-      <c r="DT4" t="inlineStr"/>
-      <c r="DU4" t="inlineStr"/>
-      <c r="DV4" t="inlineStr"/>
-      <c r="DW4" t="inlineStr"/>
-      <c r="DX4" t="inlineStr"/>
-      <c r="DY4" t="inlineStr"/>
-      <c r="DZ4" t="inlineStr"/>
-      <c r="EA4" t="inlineStr"/>
-      <c r="EB4" t="inlineStr"/>
-      <c r="EC4" t="inlineStr"/>
-      <c r="ED4" t="inlineStr"/>
-      <c r="EE4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>1690</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3400</v>
+      </c>
+      <c r="N4" t="n">
+        <v>11280</v>
+      </c>
+      <c r="O4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>47700</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>51200</v>
+      </c>
+      <c r="R4" t="n">
+        <v>17400</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8800</v>
+      </c>
+      <c r="T4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>820</v>
+      </c>
+      <c r="V4" t="n">
+        <v>33000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>9500</v>
+      </c>
+      <c r="X4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>5800</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4100</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>110000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>131800</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>147100</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>5300</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3800</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>3700</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>7100</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1650</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2100</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>6400</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>410</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>24100</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>43000</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4700</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>9800</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2300</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1640</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>10100</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1350</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>24600</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>41000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>61000</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>5130</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>11800</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>16900</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1400</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>17400</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1540</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>12700</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>2500</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>6860</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>2760</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>3300</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>3200</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>22650</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>14000</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>13500</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>1900</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>1450</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>600</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>51000</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>1800</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>1400</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>2100</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>1100</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>600</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>5800</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>6600</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>1550</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>3600</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>2670</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>6100</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>74900</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>52000</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>900</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>3380</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>5100</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>5900</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>3400</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>1690</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>3800</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>195000</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>820</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>1700</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>7200</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>3500</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>3650</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>2300</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2607,130 +2855,378 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
-      <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr"/>
-      <c r="BW5" t="inlineStr"/>
-      <c r="BX5" t="inlineStr"/>
-      <c r="BY5" t="inlineStr"/>
-      <c r="BZ5" t="inlineStr"/>
-      <c r="CA5" t="inlineStr"/>
-      <c r="CB5" t="inlineStr"/>
-      <c r="CC5" t="inlineStr"/>
-      <c r="CD5" t="inlineStr"/>
-      <c r="CE5" t="inlineStr"/>
-      <c r="CF5" t="inlineStr"/>
-      <c r="CG5" t="inlineStr"/>
-      <c r="CH5" t="inlineStr"/>
-      <c r="CI5" t="inlineStr"/>
-      <c r="CJ5" t="inlineStr"/>
-      <c r="CK5" t="inlineStr"/>
-      <c r="CL5" t="inlineStr"/>
-      <c r="CM5" t="inlineStr"/>
-      <c r="CN5" t="inlineStr"/>
-      <c r="CO5" t="inlineStr"/>
-      <c r="CP5" t="inlineStr"/>
-      <c r="CQ5" t="inlineStr"/>
-      <c r="CR5" t="inlineStr"/>
-      <c r="CS5" t="inlineStr"/>
-      <c r="CT5" t="inlineStr"/>
-      <c r="CU5" t="inlineStr"/>
-      <c r="CV5" t="inlineStr"/>
-      <c r="CW5" t="inlineStr"/>
-      <c r="CX5" t="inlineStr"/>
-      <c r="CY5" t="inlineStr"/>
-      <c r="CZ5" t="inlineStr"/>
-      <c r="DA5" t="inlineStr"/>
-      <c r="DB5" t="inlineStr"/>
-      <c r="DC5" t="inlineStr"/>
-      <c r="DD5" t="inlineStr"/>
-      <c r="DE5" t="inlineStr"/>
-      <c r="DF5" t="inlineStr"/>
-      <c r="DG5" t="inlineStr"/>
-      <c r="DH5" t="inlineStr"/>
-      <c r="DI5" t="inlineStr"/>
-      <c r="DJ5" t="inlineStr"/>
-      <c r="DK5" t="inlineStr"/>
-      <c r="DL5" t="inlineStr"/>
-      <c r="DM5" t="inlineStr"/>
-      <c r="DN5" t="inlineStr"/>
-      <c r="DO5" t="inlineStr"/>
-      <c r="DP5" t="inlineStr"/>
-      <c r="DQ5" t="inlineStr"/>
-      <c r="DR5" t="inlineStr"/>
-      <c r="DS5" t="inlineStr"/>
-      <c r="DT5" t="inlineStr"/>
-      <c r="DU5" t="inlineStr"/>
-      <c r="DV5" t="inlineStr"/>
-      <c r="DW5" t="inlineStr"/>
-      <c r="DX5" t="inlineStr"/>
-      <c r="DY5" t="inlineStr"/>
-      <c r="DZ5" t="inlineStr"/>
-      <c r="EA5" t="inlineStr"/>
-      <c r="EB5" t="inlineStr"/>
-      <c r="EC5" t="inlineStr"/>
-      <c r="ED5" t="inlineStr"/>
-      <c r="EE5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>1690</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3400</v>
+      </c>
+      <c r="N5" t="n">
+        <v>11280</v>
+      </c>
+      <c r="O5" t="n">
+        <v>20000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>47700</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>51200</v>
+      </c>
+      <c r="R5" t="n">
+        <v>17400</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8800</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>820</v>
+      </c>
+      <c r="V5" t="n">
+        <v>33000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>9500</v>
+      </c>
+      <c r="X5" t="n">
+        <v>6500</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4100</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>110000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>131800</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>147100</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>5300</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3800</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>3700</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>7100</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1650</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2100</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>6400</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>410</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>24100</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>43000</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4700</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>9800</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2300</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1640</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>10100</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1350</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>24600</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2200</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>41000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>61000</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>5130</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>11800</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>16900</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1400</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>17400</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1540</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>12700</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>6860</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>2760</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>2200</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>3300</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>22650</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>14000</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>13500</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>1900</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>1450</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>600</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>51000</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>1400</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>2100</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>20000</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>1100</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>600</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>6600</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>1550</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>3600</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>2670</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>6100</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>74900</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>52000</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>900</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>3380</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>5900</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>3400</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>1690</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>3800</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>195000</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>820</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>1700</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>7200</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>3650</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>2300</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2750,130 +3246,378 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
-      <c r="BW6" t="inlineStr"/>
-      <c r="BX6" t="inlineStr"/>
-      <c r="BY6" t="inlineStr"/>
-      <c r="BZ6" t="inlineStr"/>
-      <c r="CA6" t="inlineStr"/>
-      <c r="CB6" t="inlineStr"/>
-      <c r="CC6" t="inlineStr"/>
-      <c r="CD6" t="inlineStr"/>
-      <c r="CE6" t="inlineStr"/>
-      <c r="CF6" t="inlineStr"/>
-      <c r="CG6" t="inlineStr"/>
-      <c r="CH6" t="inlineStr"/>
-      <c r="CI6" t="inlineStr"/>
-      <c r="CJ6" t="inlineStr"/>
-      <c r="CK6" t="inlineStr"/>
-      <c r="CL6" t="inlineStr"/>
-      <c r="CM6" t="inlineStr"/>
-      <c r="CN6" t="inlineStr"/>
-      <c r="CO6" t="inlineStr"/>
-      <c r="CP6" t="inlineStr"/>
-      <c r="CQ6" t="inlineStr"/>
-      <c r="CR6" t="inlineStr"/>
-      <c r="CS6" t="inlineStr"/>
-      <c r="CT6" t="inlineStr"/>
-      <c r="CU6" t="inlineStr"/>
-      <c r="CV6" t="inlineStr"/>
-      <c r="CW6" t="inlineStr"/>
-      <c r="CX6" t="inlineStr"/>
-      <c r="CY6" t="inlineStr"/>
-      <c r="CZ6" t="inlineStr"/>
-      <c r="DA6" t="inlineStr"/>
-      <c r="DB6" t="inlineStr"/>
-      <c r="DC6" t="inlineStr"/>
-      <c r="DD6" t="inlineStr"/>
-      <c r="DE6" t="inlineStr"/>
-      <c r="DF6" t="inlineStr"/>
-      <c r="DG6" t="inlineStr"/>
-      <c r="DH6" t="inlineStr"/>
-      <c r="DI6" t="inlineStr"/>
-      <c r="DJ6" t="inlineStr"/>
-      <c r="DK6" t="inlineStr"/>
-      <c r="DL6" t="inlineStr"/>
-      <c r="DM6" t="inlineStr"/>
-      <c r="DN6" t="inlineStr"/>
-      <c r="DO6" t="inlineStr"/>
-      <c r="DP6" t="inlineStr"/>
-      <c r="DQ6" t="inlineStr"/>
-      <c r="DR6" t="inlineStr"/>
-      <c r="DS6" t="inlineStr"/>
-      <c r="DT6" t="inlineStr"/>
-      <c r="DU6" t="inlineStr"/>
-      <c r="DV6" t="inlineStr"/>
-      <c r="DW6" t="inlineStr"/>
-      <c r="DX6" t="inlineStr"/>
-      <c r="DY6" t="inlineStr"/>
-      <c r="DZ6" t="inlineStr"/>
-      <c r="EA6" t="inlineStr"/>
-      <c r="EB6" t="inlineStr"/>
-      <c r="EC6" t="inlineStr"/>
-      <c r="ED6" t="inlineStr"/>
-      <c r="EE6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>1690</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3400</v>
+      </c>
+      <c r="N6" t="n">
+        <v>11280</v>
+      </c>
+      <c r="O6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>47700</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>51200</v>
+      </c>
+      <c r="R6" t="n">
+        <v>17400</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8800</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>820</v>
+      </c>
+      <c r="V6" t="n">
+        <v>33000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>9500</v>
+      </c>
+      <c r="X6" t="n">
+        <v>6500</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>5800</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4100</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>110000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>131800</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>147100</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>5300</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3800</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3700</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>7100</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1650</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2100</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>6400</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>410</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>24100</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>43000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4700</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>9800</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2400</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2300</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1640</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>10100</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1350</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>24600</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2200</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>41000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>61000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>5130</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>11800</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>16900</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>17400</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1540</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>12700</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>2400</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>6860</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>2760</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>2200</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>3300</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>3200</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>22650</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>14000</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>13500</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>1900</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>1450</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>600</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>51000</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>2100</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>600</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>5800</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>6600</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>1550</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>3600</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>2670</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>6100</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>74900</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>52000</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>900</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>3380</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>5100</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>5900</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>3400</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>1690</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>3800</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>195000</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>820</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>1700</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>7200</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>3650</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>2300</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3284,130 +4028,378 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
-      <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr"/>
-      <c r="BR8" t="inlineStr"/>
-      <c r="BS8" t="inlineStr"/>
-      <c r="BT8" t="inlineStr"/>
-      <c r="BU8" t="inlineStr"/>
-      <c r="BV8" t="inlineStr"/>
-      <c r="BW8" t="inlineStr"/>
-      <c r="BX8" t="inlineStr"/>
-      <c r="BY8" t="inlineStr"/>
-      <c r="BZ8" t="inlineStr"/>
-      <c r="CA8" t="inlineStr"/>
-      <c r="CB8" t="inlineStr"/>
-      <c r="CC8" t="inlineStr"/>
-      <c r="CD8" t="inlineStr"/>
-      <c r="CE8" t="inlineStr"/>
-      <c r="CF8" t="inlineStr"/>
-      <c r="CG8" t="inlineStr"/>
-      <c r="CH8" t="inlineStr"/>
-      <c r="CI8" t="inlineStr"/>
-      <c r="CJ8" t="inlineStr"/>
-      <c r="CK8" t="inlineStr"/>
-      <c r="CL8" t="inlineStr"/>
-      <c r="CM8" t="inlineStr"/>
-      <c r="CN8" t="inlineStr"/>
-      <c r="CO8" t="inlineStr"/>
-      <c r="CP8" t="inlineStr"/>
-      <c r="CQ8" t="inlineStr"/>
-      <c r="CR8" t="inlineStr"/>
-      <c r="CS8" t="inlineStr"/>
-      <c r="CT8" t="inlineStr"/>
-      <c r="CU8" t="inlineStr"/>
-      <c r="CV8" t="inlineStr"/>
-      <c r="CW8" t="inlineStr"/>
-      <c r="CX8" t="inlineStr"/>
-      <c r="CY8" t="inlineStr"/>
-      <c r="CZ8" t="inlineStr"/>
-      <c r="DA8" t="inlineStr"/>
-      <c r="DB8" t="inlineStr"/>
-      <c r="DC8" t="inlineStr"/>
-      <c r="DD8" t="inlineStr"/>
-      <c r="DE8" t="inlineStr"/>
-      <c r="DF8" t="inlineStr"/>
-      <c r="DG8" t="inlineStr"/>
-      <c r="DH8" t="inlineStr"/>
-      <c r="DI8" t="inlineStr"/>
-      <c r="DJ8" t="inlineStr"/>
-      <c r="DK8" t="inlineStr"/>
-      <c r="DL8" t="inlineStr"/>
-      <c r="DM8" t="inlineStr"/>
-      <c r="DN8" t="inlineStr"/>
-      <c r="DO8" t="inlineStr"/>
-      <c r="DP8" t="inlineStr"/>
-      <c r="DQ8" t="inlineStr"/>
-      <c r="DR8" t="inlineStr"/>
-      <c r="DS8" t="inlineStr"/>
-      <c r="DT8" t="inlineStr"/>
-      <c r="DU8" t="inlineStr"/>
-      <c r="DV8" t="inlineStr"/>
-      <c r="DW8" t="inlineStr"/>
-      <c r="DX8" t="inlineStr"/>
-      <c r="DY8" t="inlineStr"/>
-      <c r="DZ8" t="inlineStr"/>
-      <c r="EA8" t="inlineStr"/>
-      <c r="EB8" t="inlineStr"/>
-      <c r="EC8" t="inlineStr"/>
-      <c r="ED8" t="inlineStr"/>
-      <c r="EE8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>1690</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3400</v>
+      </c>
+      <c r="N8" t="n">
+        <v>11280</v>
+      </c>
+      <c r="O8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="P8" t="n">
+        <v>47700</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>51200</v>
+      </c>
+      <c r="R8" t="n">
+        <v>17400</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8800</v>
+      </c>
+      <c r="T8" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U8" t="n">
+        <v>820</v>
+      </c>
+      <c r="V8" t="n">
+        <v>33000</v>
+      </c>
+      <c r="W8" t="n">
+        <v>9500</v>
+      </c>
+      <c r="X8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5800</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4100</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>110000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>131800</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>147100</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>5300</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3800</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>3700</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>7100</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1650</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2100</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>6400</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>410</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>24100</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>43000</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4700</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>9800</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2400</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2300</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1640</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>10100</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1350</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>24600</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2200</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>41000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>61000</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>5130</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>11800</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>16900</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1400</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>17400</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1540</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>12700</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>2400</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>1600</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>6860</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>2760</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>2200</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>3300</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>3200</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>22650</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>14000</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>13500</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>1900</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>1450</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>600</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>51000</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>1400</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>2100</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>1100</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>600</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>5800</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>6600</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>1550</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>1600</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>3600</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>2670</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>6100</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>74900</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>52000</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>900</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>3380</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>5100</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>5900</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>3400</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>1690</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>3800</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>195000</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>820</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>1700</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>7200</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>3500</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>3650</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>2300</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3427,130 +4419,378 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
-      <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="inlineStr"/>
-      <c r="BX9" t="inlineStr"/>
-      <c r="BY9" t="inlineStr"/>
-      <c r="BZ9" t="inlineStr"/>
-      <c r="CA9" t="inlineStr"/>
-      <c r="CB9" t="inlineStr"/>
-      <c r="CC9" t="inlineStr"/>
-      <c r="CD9" t="inlineStr"/>
-      <c r="CE9" t="inlineStr"/>
-      <c r="CF9" t="inlineStr"/>
-      <c r="CG9" t="inlineStr"/>
-      <c r="CH9" t="inlineStr"/>
-      <c r="CI9" t="inlineStr"/>
-      <c r="CJ9" t="inlineStr"/>
-      <c r="CK9" t="inlineStr"/>
-      <c r="CL9" t="inlineStr"/>
-      <c r="CM9" t="inlineStr"/>
-      <c r="CN9" t="inlineStr"/>
-      <c r="CO9" t="inlineStr"/>
-      <c r="CP9" t="inlineStr"/>
-      <c r="CQ9" t="inlineStr"/>
-      <c r="CR9" t="inlineStr"/>
-      <c r="CS9" t="inlineStr"/>
-      <c r="CT9" t="inlineStr"/>
-      <c r="CU9" t="inlineStr"/>
-      <c r="CV9" t="inlineStr"/>
-      <c r="CW9" t="inlineStr"/>
-      <c r="CX9" t="inlineStr"/>
-      <c r="CY9" t="inlineStr"/>
-      <c r="CZ9" t="inlineStr"/>
-      <c r="DA9" t="inlineStr"/>
-      <c r="DB9" t="inlineStr"/>
-      <c r="DC9" t="inlineStr"/>
-      <c r="DD9" t="inlineStr"/>
-      <c r="DE9" t="inlineStr"/>
-      <c r="DF9" t="inlineStr"/>
-      <c r="DG9" t="inlineStr"/>
-      <c r="DH9" t="inlineStr"/>
-      <c r="DI9" t="inlineStr"/>
-      <c r="DJ9" t="inlineStr"/>
-      <c r="DK9" t="inlineStr"/>
-      <c r="DL9" t="inlineStr"/>
-      <c r="DM9" t="inlineStr"/>
-      <c r="DN9" t="inlineStr"/>
-      <c r="DO9" t="inlineStr"/>
-      <c r="DP9" t="inlineStr"/>
-      <c r="DQ9" t="inlineStr"/>
-      <c r="DR9" t="inlineStr"/>
-      <c r="DS9" t="inlineStr"/>
-      <c r="DT9" t="inlineStr"/>
-      <c r="DU9" t="inlineStr"/>
-      <c r="DV9" t="inlineStr"/>
-      <c r="DW9" t="inlineStr"/>
-      <c r="DX9" t="inlineStr"/>
-      <c r="DY9" t="inlineStr"/>
-      <c r="DZ9" t="inlineStr"/>
-      <c r="EA9" t="inlineStr"/>
-      <c r="EB9" t="inlineStr"/>
-      <c r="EC9" t="inlineStr"/>
-      <c r="ED9" t="inlineStr"/>
-      <c r="EE9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>1690</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3400</v>
+      </c>
+      <c r="N9" t="n">
+        <v>11280</v>
+      </c>
+      <c r="O9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="P9" t="n">
+        <v>47700</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>51200</v>
+      </c>
+      <c r="R9" t="n">
+        <v>17400</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8800</v>
+      </c>
+      <c r="T9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U9" t="n">
+        <v>820</v>
+      </c>
+      <c r="V9" t="n">
+        <v>33000</v>
+      </c>
+      <c r="W9" t="n">
+        <v>9500</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6500</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5800</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4100</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>110000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>131800</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>147100</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>5300</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3800</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>3700</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>7100</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1650</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2100</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>6400</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>410</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>24100</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>43000</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4700</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>9800</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2400</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2300</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1640</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>10100</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1350</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>24600</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>41000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>61000</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>5130</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>11800</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>16900</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1400</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>17400</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>4000</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1540</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>12700</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>2400</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>6860</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>2760</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>3300</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>3200</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>22650</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>14000</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>13500</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>1900</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>1450</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>600</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>51000</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>1400</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>2100</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>1100</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>600</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>5800</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>6600</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>1550</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>3600</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>2670</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>6100</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>74900</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>52000</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>900</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>3380</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>5100</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>5900</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>3400</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>1690</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>3800</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>195000</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>820</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>1700</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>7200</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>3650</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>2300</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3570,130 +4810,378 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
-      <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr"/>
-      <c r="BQ10" t="inlineStr"/>
-      <c r="BR10" t="inlineStr"/>
-      <c r="BS10" t="inlineStr"/>
-      <c r="BT10" t="inlineStr"/>
-      <c r="BU10" t="inlineStr"/>
-      <c r="BV10" t="inlineStr"/>
-      <c r="BW10" t="inlineStr"/>
-      <c r="BX10" t="inlineStr"/>
-      <c r="BY10" t="inlineStr"/>
-      <c r="BZ10" t="inlineStr"/>
-      <c r="CA10" t="inlineStr"/>
-      <c r="CB10" t="inlineStr"/>
-      <c r="CC10" t="inlineStr"/>
-      <c r="CD10" t="inlineStr"/>
-      <c r="CE10" t="inlineStr"/>
-      <c r="CF10" t="inlineStr"/>
-      <c r="CG10" t="inlineStr"/>
-      <c r="CH10" t="inlineStr"/>
-      <c r="CI10" t="inlineStr"/>
-      <c r="CJ10" t="inlineStr"/>
-      <c r="CK10" t="inlineStr"/>
-      <c r="CL10" t="inlineStr"/>
-      <c r="CM10" t="inlineStr"/>
-      <c r="CN10" t="inlineStr"/>
-      <c r="CO10" t="inlineStr"/>
-      <c r="CP10" t="inlineStr"/>
-      <c r="CQ10" t="inlineStr"/>
-      <c r="CR10" t="inlineStr"/>
-      <c r="CS10" t="inlineStr"/>
-      <c r="CT10" t="inlineStr"/>
-      <c r="CU10" t="inlineStr"/>
-      <c r="CV10" t="inlineStr"/>
-      <c r="CW10" t="inlineStr"/>
-      <c r="CX10" t="inlineStr"/>
-      <c r="CY10" t="inlineStr"/>
-      <c r="CZ10" t="inlineStr"/>
-      <c r="DA10" t="inlineStr"/>
-      <c r="DB10" t="inlineStr"/>
-      <c r="DC10" t="inlineStr"/>
-      <c r="DD10" t="inlineStr"/>
-      <c r="DE10" t="inlineStr"/>
-      <c r="DF10" t="inlineStr"/>
-      <c r="DG10" t="inlineStr"/>
-      <c r="DH10" t="inlineStr"/>
-      <c r="DI10" t="inlineStr"/>
-      <c r="DJ10" t="inlineStr"/>
-      <c r="DK10" t="inlineStr"/>
-      <c r="DL10" t="inlineStr"/>
-      <c r="DM10" t="inlineStr"/>
-      <c r="DN10" t="inlineStr"/>
-      <c r="DO10" t="inlineStr"/>
-      <c r="DP10" t="inlineStr"/>
-      <c r="DQ10" t="inlineStr"/>
-      <c r="DR10" t="inlineStr"/>
-      <c r="DS10" t="inlineStr"/>
-      <c r="DT10" t="inlineStr"/>
-      <c r="DU10" t="inlineStr"/>
-      <c r="DV10" t="inlineStr"/>
-      <c r="DW10" t="inlineStr"/>
-      <c r="DX10" t="inlineStr"/>
-      <c r="DY10" t="inlineStr"/>
-      <c r="DZ10" t="inlineStr"/>
-      <c r="EA10" t="inlineStr"/>
-      <c r="EB10" t="inlineStr"/>
-      <c r="EC10" t="inlineStr"/>
-      <c r="ED10" t="inlineStr"/>
-      <c r="EE10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>1690</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3400</v>
+      </c>
+      <c r="N10" t="n">
+        <v>11280</v>
+      </c>
+      <c r="O10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="P10" t="n">
+        <v>47700</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>51200</v>
+      </c>
+      <c r="R10" t="n">
+        <v>17400</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8800</v>
+      </c>
+      <c r="T10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U10" t="n">
+        <v>820</v>
+      </c>
+      <c r="V10" t="n">
+        <v>33000</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9500</v>
+      </c>
+      <c r="X10" t="n">
+        <v>6500</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>5800</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4100</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>110000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>131800</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>147100</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>5300</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3800</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>3700</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>7100</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1650</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2100</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>6400</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>410</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>24100</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>43000</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4700</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>9800</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2400</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2300</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1640</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>10100</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1350</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>24600</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2200</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>41000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>61000</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>5130</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>11800</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>16900</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1400</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>17400</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1540</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>12700</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>2400</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>1600</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>6860</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>2760</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>2200</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>3300</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>3200</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>22650</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>14000</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>13500</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>1900</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>1450</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>600</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>51000</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>1400</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>2100</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>1100</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>600</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>5800</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>6600</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>1550</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>1600</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>3600</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>2670</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>15000</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>6100</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>74900</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>52000</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>900</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>3380</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>5100</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>5900</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>3400</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>1690</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>3800</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>195000</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>820</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>1700</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>7200</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>3500</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>3650</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>2300</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3713,130 +5201,378 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="inlineStr"/>
-      <c r="BK11" t="inlineStr"/>
-      <c r="BL11" t="inlineStr"/>
-      <c r="BM11" t="inlineStr"/>
-      <c r="BN11" t="inlineStr"/>
-      <c r="BO11" t="inlineStr"/>
-      <c r="BP11" t="inlineStr"/>
-      <c r="BQ11" t="inlineStr"/>
-      <c r="BR11" t="inlineStr"/>
-      <c r="BS11" t="inlineStr"/>
-      <c r="BT11" t="inlineStr"/>
-      <c r="BU11" t="inlineStr"/>
-      <c r="BV11" t="inlineStr"/>
-      <c r="BW11" t="inlineStr"/>
-      <c r="BX11" t="inlineStr"/>
-      <c r="BY11" t="inlineStr"/>
-      <c r="BZ11" t="inlineStr"/>
-      <c r="CA11" t="inlineStr"/>
-      <c r="CB11" t="inlineStr"/>
-      <c r="CC11" t="inlineStr"/>
-      <c r="CD11" t="inlineStr"/>
-      <c r="CE11" t="inlineStr"/>
-      <c r="CF11" t="inlineStr"/>
-      <c r="CG11" t="inlineStr"/>
-      <c r="CH11" t="inlineStr"/>
-      <c r="CI11" t="inlineStr"/>
-      <c r="CJ11" t="inlineStr"/>
-      <c r="CK11" t="inlineStr"/>
-      <c r="CL11" t="inlineStr"/>
-      <c r="CM11" t="inlineStr"/>
-      <c r="CN11" t="inlineStr"/>
-      <c r="CO11" t="inlineStr"/>
-      <c r="CP11" t="inlineStr"/>
-      <c r="CQ11" t="inlineStr"/>
-      <c r="CR11" t="inlineStr"/>
-      <c r="CS11" t="inlineStr"/>
-      <c r="CT11" t="inlineStr"/>
-      <c r="CU11" t="inlineStr"/>
-      <c r="CV11" t="inlineStr"/>
-      <c r="CW11" t="inlineStr"/>
-      <c r="CX11" t="inlineStr"/>
-      <c r="CY11" t="inlineStr"/>
-      <c r="CZ11" t="inlineStr"/>
-      <c r="DA11" t="inlineStr"/>
-      <c r="DB11" t="inlineStr"/>
-      <c r="DC11" t="inlineStr"/>
-      <c r="DD11" t="inlineStr"/>
-      <c r="DE11" t="inlineStr"/>
-      <c r="DF11" t="inlineStr"/>
-      <c r="DG11" t="inlineStr"/>
-      <c r="DH11" t="inlineStr"/>
-      <c r="DI11" t="inlineStr"/>
-      <c r="DJ11" t="inlineStr"/>
-      <c r="DK11" t="inlineStr"/>
-      <c r="DL11" t="inlineStr"/>
-      <c r="DM11" t="inlineStr"/>
-      <c r="DN11" t="inlineStr"/>
-      <c r="DO11" t="inlineStr"/>
-      <c r="DP11" t="inlineStr"/>
-      <c r="DQ11" t="inlineStr"/>
-      <c r="DR11" t="inlineStr"/>
-      <c r="DS11" t="inlineStr"/>
-      <c r="DT11" t="inlineStr"/>
-      <c r="DU11" t="inlineStr"/>
-      <c r="DV11" t="inlineStr"/>
-      <c r="DW11" t="inlineStr"/>
-      <c r="DX11" t="inlineStr"/>
-      <c r="DY11" t="inlineStr"/>
-      <c r="DZ11" t="inlineStr"/>
-      <c r="EA11" t="inlineStr"/>
-      <c r="EB11" t="inlineStr"/>
-      <c r="EC11" t="inlineStr"/>
-      <c r="ED11" t="inlineStr"/>
-      <c r="EE11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>1690</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3400</v>
+      </c>
+      <c r="N11" t="n">
+        <v>11280</v>
+      </c>
+      <c r="O11" t="n">
+        <v>20000</v>
+      </c>
+      <c r="P11" t="n">
+        <v>47700</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>51200</v>
+      </c>
+      <c r="R11" t="n">
+        <v>17400</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8800</v>
+      </c>
+      <c r="T11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U11" t="n">
+        <v>820</v>
+      </c>
+      <c r="V11" t="n">
+        <v>33000</v>
+      </c>
+      <c r="W11" t="n">
+        <v>9500</v>
+      </c>
+      <c r="X11" t="n">
+        <v>6500</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5800</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4100</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>110000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>131800</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>147100</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>5300</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3800</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>3700</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>7100</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1650</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2100</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>6400</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>410</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>24100</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>43000</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4700</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9800</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>2300</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1640</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>10100</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1350</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>24600</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2200</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>41000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>61000</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>5130</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>11800</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>16900</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1400</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>17400</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1540</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>12700</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>6860</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>2760</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>2200</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>3300</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>3200</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>22650</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>14000</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>13500</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>1900</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>1450</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>600</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>1500</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>51000</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>1400</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>2100</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>20000</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>1100</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>600</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>5800</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>6600</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>1550</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>3600</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>2670</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>15000</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>6100</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>74900</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>52000</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>900</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>3380</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>5100</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>5900</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>3400</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>1690</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>3800</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>195000</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>820</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>1700</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>7200</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>3500</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>3650</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>2300</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3856,130 +5592,378 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr"/>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="inlineStr"/>
-      <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="inlineStr"/>
-      <c r="BN12" t="inlineStr"/>
-      <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr"/>
-      <c r="BQ12" t="inlineStr"/>
-      <c r="BR12" t="inlineStr"/>
-      <c r="BS12" t="inlineStr"/>
-      <c r="BT12" t="inlineStr"/>
-      <c r="BU12" t="inlineStr"/>
-      <c r="BV12" t="inlineStr"/>
-      <c r="BW12" t="inlineStr"/>
-      <c r="BX12" t="inlineStr"/>
-      <c r="BY12" t="inlineStr"/>
-      <c r="BZ12" t="inlineStr"/>
-      <c r="CA12" t="inlineStr"/>
-      <c r="CB12" t="inlineStr"/>
-      <c r="CC12" t="inlineStr"/>
-      <c r="CD12" t="inlineStr"/>
-      <c r="CE12" t="inlineStr"/>
-      <c r="CF12" t="inlineStr"/>
-      <c r="CG12" t="inlineStr"/>
-      <c r="CH12" t="inlineStr"/>
-      <c r="CI12" t="inlineStr"/>
-      <c r="CJ12" t="inlineStr"/>
-      <c r="CK12" t="inlineStr"/>
-      <c r="CL12" t="inlineStr"/>
-      <c r="CM12" t="inlineStr"/>
-      <c r="CN12" t="inlineStr"/>
-      <c r="CO12" t="inlineStr"/>
-      <c r="CP12" t="inlineStr"/>
-      <c r="CQ12" t="inlineStr"/>
-      <c r="CR12" t="inlineStr"/>
-      <c r="CS12" t="inlineStr"/>
-      <c r="CT12" t="inlineStr"/>
-      <c r="CU12" t="inlineStr"/>
-      <c r="CV12" t="inlineStr"/>
-      <c r="CW12" t="inlineStr"/>
-      <c r="CX12" t="inlineStr"/>
-      <c r="CY12" t="inlineStr"/>
-      <c r="CZ12" t="inlineStr"/>
-      <c r="DA12" t="inlineStr"/>
-      <c r="DB12" t="inlineStr"/>
-      <c r="DC12" t="inlineStr"/>
-      <c r="DD12" t="inlineStr"/>
-      <c r="DE12" t="inlineStr"/>
-      <c r="DF12" t="inlineStr"/>
-      <c r="DG12" t="inlineStr"/>
-      <c r="DH12" t="inlineStr"/>
-      <c r="DI12" t="inlineStr"/>
-      <c r="DJ12" t="inlineStr"/>
-      <c r="DK12" t="inlineStr"/>
-      <c r="DL12" t="inlineStr"/>
-      <c r="DM12" t="inlineStr"/>
-      <c r="DN12" t="inlineStr"/>
-      <c r="DO12" t="inlineStr"/>
-      <c r="DP12" t="inlineStr"/>
-      <c r="DQ12" t="inlineStr"/>
-      <c r="DR12" t="inlineStr"/>
-      <c r="DS12" t="inlineStr"/>
-      <c r="DT12" t="inlineStr"/>
-      <c r="DU12" t="inlineStr"/>
-      <c r="DV12" t="inlineStr"/>
-      <c r="DW12" t="inlineStr"/>
-      <c r="DX12" t="inlineStr"/>
-      <c r="DY12" t="inlineStr"/>
-      <c r="DZ12" t="inlineStr"/>
-      <c r="EA12" t="inlineStr"/>
-      <c r="EB12" t="inlineStr"/>
-      <c r="EC12" t="inlineStr"/>
-      <c r="ED12" t="inlineStr"/>
-      <c r="EE12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>1690</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3400</v>
+      </c>
+      <c r="N12" t="n">
+        <v>11280</v>
+      </c>
+      <c r="O12" t="n">
+        <v>20000</v>
+      </c>
+      <c r="P12" t="n">
+        <v>47700</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>51200</v>
+      </c>
+      <c r="R12" t="n">
+        <v>17400</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8800</v>
+      </c>
+      <c r="T12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U12" t="n">
+        <v>820</v>
+      </c>
+      <c r="V12" t="n">
+        <v>33000</v>
+      </c>
+      <c r="W12" t="n">
+        <v>9500</v>
+      </c>
+      <c r="X12" t="n">
+        <v>6500</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>5800</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4100</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>110000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>131800</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>147100</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>5300</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3800</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>3700</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>7100</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1650</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2100</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>6400</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>410</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>24100</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>43000</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4700</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>9800</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2400</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2300</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1640</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>10100</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1350</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>24600</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2200</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>41000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>61000</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>5130</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>11800</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>16900</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1400</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>17400</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>4000</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1540</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>12700</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>2400</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>1600</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>6860</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>2760</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>2200</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>3300</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>3200</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>22650</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>14000</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>13500</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>1900</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>1450</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>600</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>51000</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>1400</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>2100</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>20000</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>1100</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>600</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>5800</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>6600</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>1550</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>1600</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>3600</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>2670</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>15000</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>6100</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>74900</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>52000</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>900</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>3380</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>5100</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>5900</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>3400</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>1690</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>3800</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>195000</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>820</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>1700</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>7200</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>3500</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>3650</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>2300</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3999,130 +5983,378 @@
         <v>100000</v>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
-      <c r="BI13" t="inlineStr"/>
-      <c r="BJ13" t="inlineStr"/>
-      <c r="BK13" t="inlineStr"/>
-      <c r="BL13" t="inlineStr"/>
-      <c r="BM13" t="inlineStr"/>
-      <c r="BN13" t="inlineStr"/>
-      <c r="BO13" t="inlineStr"/>
-      <c r="BP13" t="inlineStr"/>
-      <c r="BQ13" t="inlineStr"/>
-      <c r="BR13" t="inlineStr"/>
-      <c r="BS13" t="inlineStr"/>
-      <c r="BT13" t="inlineStr"/>
-      <c r="BU13" t="inlineStr"/>
-      <c r="BV13" t="inlineStr"/>
-      <c r="BW13" t="inlineStr"/>
-      <c r="BX13" t="inlineStr"/>
-      <c r="BY13" t="inlineStr"/>
-      <c r="BZ13" t="inlineStr"/>
-      <c r="CA13" t="inlineStr"/>
-      <c r="CB13" t="inlineStr"/>
-      <c r="CC13" t="inlineStr"/>
-      <c r="CD13" t="inlineStr"/>
-      <c r="CE13" t="inlineStr"/>
-      <c r="CF13" t="inlineStr"/>
-      <c r="CG13" t="inlineStr"/>
-      <c r="CH13" t="inlineStr"/>
-      <c r="CI13" t="inlineStr"/>
-      <c r="CJ13" t="inlineStr"/>
-      <c r="CK13" t="inlineStr"/>
-      <c r="CL13" t="inlineStr"/>
-      <c r="CM13" t="inlineStr"/>
-      <c r="CN13" t="inlineStr"/>
-      <c r="CO13" t="inlineStr"/>
-      <c r="CP13" t="inlineStr"/>
-      <c r="CQ13" t="inlineStr"/>
-      <c r="CR13" t="inlineStr"/>
-      <c r="CS13" t="inlineStr"/>
-      <c r="CT13" t="inlineStr"/>
-      <c r="CU13" t="inlineStr"/>
-      <c r="CV13" t="inlineStr"/>
-      <c r="CW13" t="inlineStr"/>
-      <c r="CX13" t="inlineStr"/>
-      <c r="CY13" t="inlineStr"/>
-      <c r="CZ13" t="inlineStr"/>
-      <c r="DA13" t="inlineStr"/>
-      <c r="DB13" t="inlineStr"/>
-      <c r="DC13" t="inlineStr"/>
-      <c r="DD13" t="inlineStr"/>
-      <c r="DE13" t="inlineStr"/>
-      <c r="DF13" t="inlineStr"/>
-      <c r="DG13" t="inlineStr"/>
-      <c r="DH13" t="inlineStr"/>
-      <c r="DI13" t="inlineStr"/>
-      <c r="DJ13" t="inlineStr"/>
-      <c r="DK13" t="inlineStr"/>
-      <c r="DL13" t="inlineStr"/>
-      <c r="DM13" t="inlineStr"/>
-      <c r="DN13" t="inlineStr"/>
-      <c r="DO13" t="inlineStr"/>
-      <c r="DP13" t="inlineStr"/>
-      <c r="DQ13" t="inlineStr"/>
-      <c r="DR13" t="inlineStr"/>
-      <c r="DS13" t="inlineStr"/>
-      <c r="DT13" t="inlineStr"/>
-      <c r="DU13" t="inlineStr"/>
-      <c r="DV13" t="inlineStr"/>
-      <c r="DW13" t="inlineStr"/>
-      <c r="DX13" t="inlineStr"/>
-      <c r="DY13" t="inlineStr"/>
-      <c r="DZ13" t="inlineStr"/>
-      <c r="EA13" t="inlineStr"/>
-      <c r="EB13" t="inlineStr"/>
-      <c r="EC13" t="inlineStr"/>
-      <c r="ED13" t="inlineStr"/>
-      <c r="EE13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>1690</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3400</v>
+      </c>
+      <c r="N13" t="n">
+        <v>11280</v>
+      </c>
+      <c r="O13" t="n">
+        <v>20000</v>
+      </c>
+      <c r="P13" t="n">
+        <v>47700</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>51200</v>
+      </c>
+      <c r="R13" t="n">
+        <v>17400</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8800</v>
+      </c>
+      <c r="T13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U13" t="n">
+        <v>820</v>
+      </c>
+      <c r="V13" t="n">
+        <v>33000</v>
+      </c>
+      <c r="W13" t="n">
+        <v>9500</v>
+      </c>
+      <c r="X13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>5800</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4100</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>110000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>131800</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>147100</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>5300</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3800</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>3700</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>7100</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1650</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2100</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>6400</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>410</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>24100</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>43000</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4700</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>9800</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2400</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>2300</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1640</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>10100</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1350</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>24600</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2200</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>41000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>61000</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>5130</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>11800</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>16900</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1400</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>17400</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>4000</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1540</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>12700</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>2500</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>2400</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>1600</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>6860</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>2760</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>2200</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>3300</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>3200</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>22650</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>14000</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>13500</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>1900</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>1450</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>600</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>51000</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>1800</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>1400</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>2100</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>20000</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>1100</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>600</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>5800</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>6600</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>1550</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>1600</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>3600</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>2670</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>15000</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>6100</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>74900</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>52000</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>900</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>3380</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>5100</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>5900</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>3400</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>1690</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>3800</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>195000</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>820</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>1700</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>7200</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>3500</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>3650</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>2300</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4142,130 +6374,378 @@
       <c r="K14" t="n">
         <v>150000</v>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
-      <c r="BI14" t="inlineStr"/>
-      <c r="BJ14" t="inlineStr"/>
-      <c r="BK14" t="inlineStr"/>
-      <c r="BL14" t="inlineStr"/>
-      <c r="BM14" t="inlineStr"/>
-      <c r="BN14" t="inlineStr"/>
-      <c r="BO14" t="inlineStr"/>
-      <c r="BP14" t="inlineStr"/>
-      <c r="BQ14" t="inlineStr"/>
-      <c r="BR14" t="inlineStr"/>
-      <c r="BS14" t="inlineStr"/>
-      <c r="BT14" t="inlineStr"/>
-      <c r="BU14" t="inlineStr"/>
-      <c r="BV14" t="inlineStr"/>
-      <c r="BW14" t="inlineStr"/>
-      <c r="BX14" t="inlineStr"/>
-      <c r="BY14" t="inlineStr"/>
-      <c r="BZ14" t="inlineStr"/>
-      <c r="CA14" t="inlineStr"/>
-      <c r="CB14" t="inlineStr"/>
-      <c r="CC14" t="inlineStr"/>
-      <c r="CD14" t="inlineStr"/>
-      <c r="CE14" t="inlineStr"/>
-      <c r="CF14" t="inlineStr"/>
-      <c r="CG14" t="inlineStr"/>
-      <c r="CH14" t="inlineStr"/>
-      <c r="CI14" t="inlineStr"/>
-      <c r="CJ14" t="inlineStr"/>
-      <c r="CK14" t="inlineStr"/>
-      <c r="CL14" t="inlineStr"/>
-      <c r="CM14" t="inlineStr"/>
-      <c r="CN14" t="inlineStr"/>
-      <c r="CO14" t="inlineStr"/>
-      <c r="CP14" t="inlineStr"/>
-      <c r="CQ14" t="inlineStr"/>
-      <c r="CR14" t="inlineStr"/>
-      <c r="CS14" t="inlineStr"/>
-      <c r="CT14" t="inlineStr"/>
-      <c r="CU14" t="inlineStr"/>
-      <c r="CV14" t="inlineStr"/>
-      <c r="CW14" t="inlineStr"/>
-      <c r="CX14" t="inlineStr"/>
-      <c r="CY14" t="inlineStr"/>
-      <c r="CZ14" t="inlineStr"/>
-      <c r="DA14" t="inlineStr"/>
-      <c r="DB14" t="inlineStr"/>
-      <c r="DC14" t="inlineStr"/>
-      <c r="DD14" t="inlineStr"/>
-      <c r="DE14" t="inlineStr"/>
-      <c r="DF14" t="inlineStr"/>
-      <c r="DG14" t="inlineStr"/>
-      <c r="DH14" t="inlineStr"/>
-      <c r="DI14" t="inlineStr"/>
-      <c r="DJ14" t="inlineStr"/>
-      <c r="DK14" t="inlineStr"/>
-      <c r="DL14" t="inlineStr"/>
-      <c r="DM14" t="inlineStr"/>
-      <c r="DN14" t="inlineStr"/>
-      <c r="DO14" t="inlineStr"/>
-      <c r="DP14" t="inlineStr"/>
-      <c r="DQ14" t="inlineStr"/>
-      <c r="DR14" t="inlineStr"/>
-      <c r="DS14" t="inlineStr"/>
-      <c r="DT14" t="inlineStr"/>
-      <c r="DU14" t="inlineStr"/>
-      <c r="DV14" t="inlineStr"/>
-      <c r="DW14" t="inlineStr"/>
-      <c r="DX14" t="inlineStr"/>
-      <c r="DY14" t="inlineStr"/>
-      <c r="DZ14" t="inlineStr"/>
-      <c r="EA14" t="inlineStr"/>
-      <c r="EB14" t="inlineStr"/>
-      <c r="EC14" t="inlineStr"/>
-      <c r="ED14" t="inlineStr"/>
-      <c r="EE14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>1690</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3400</v>
+      </c>
+      <c r="N14" t="n">
+        <v>11280</v>
+      </c>
+      <c r="O14" t="n">
+        <v>20000</v>
+      </c>
+      <c r="P14" t="n">
+        <v>47700</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>51200</v>
+      </c>
+      <c r="R14" t="n">
+        <v>17400</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8800</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U14" t="n">
+        <v>820</v>
+      </c>
+      <c r="V14" t="n">
+        <v>33000</v>
+      </c>
+      <c r="W14" t="n">
+        <v>9500</v>
+      </c>
+      <c r="X14" t="n">
+        <v>6500</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>5800</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4100</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>110000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>131800</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>147100</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>5300</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3800</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>3700</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>7100</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1650</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2100</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>6400</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>410</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>24100</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>43000</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4700</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>9800</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2400</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>2300</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1640</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>10100</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1350</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>24600</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2200</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>41000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>61000</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>5130</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>11800</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>16900</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1400</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>17400</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>4000</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1540</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>12700</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>2500</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>2400</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>1600</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>6860</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>2760</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>2200</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>3300</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>3200</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>22650</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>14000</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>13500</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>1900</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>1450</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>600</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>51000</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>1800</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>1400</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>2100</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>20000</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>600</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>5800</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>6600</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>1550</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>1600</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>3600</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>2670</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>6100</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>8500</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>74900</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>52000</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>900</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>3380</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>5100</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>5900</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>4000</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>7300</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>3400</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>1690</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>3800</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>195000</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>820</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>1700</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>7200</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>3500</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>3650</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>2300</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dist/data/02_Matrice_Optional_Ferretti.xlsx
+++ b/dist/data/02_Matrice_Optional_Ferretti.xlsx
@@ -6758,7 +6758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6792,6 +6792,11 @@
           <t>Nota</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Nota_IT</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6818,6 +6823,7 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6844,6 +6850,7 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6870,6 +6877,7 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6896,6 +6904,7 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6922,6 +6931,7 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6948,6 +6958,7 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6974,6 +6985,7 @@
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7000,6 +7012,7 @@
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7026,6 +7039,7 @@
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7052,6 +7066,7 @@
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7078,6 +7093,7 @@
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7108,6 +7124,11 @@
           <t>A preliminary assessment of the customer’s tender dimensions and weight is required</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>È necessaria una valutazione preliminare di dimensioni e peso del tender del cliente.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7134,6 +7155,7 @@
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7164,6 +7186,11 @@
           <t>The price refers to the Ferretti Yachts Special Edition version of the Seabob S9. Any alternative configuration will be quoted separately.</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Il prezzo si riferisce alla versione Ferretti Yachts Special Edition del Seabob S9. Qualsiasi configurazione alternativa sarà quotata a parte.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7194,6 +7221,11 @@
           <t>It includes fixing</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Include il fissaggio.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7224,6 +7256,11 @@
           <t>Including fixing</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fissaggio incluso.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7250,6 +7287,7 @@
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7276,6 +7314,7 @@
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7302,6 +7341,7 @@
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7328,6 +7368,7 @@
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7354,6 +7395,7 @@
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7380,6 +7422,7 @@
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7406,6 +7449,7 @@
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7432,6 +7476,7 @@
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7462,6 +7507,11 @@
           <t>Includes lights for staircase to flybridge and staircases to cockpit, light strips on walkways</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Include le luci della scala per il flybridge e delle scale verso il pozzetto, strisce luminose sui passavanti.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7488,6 +7538,7 @@
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7518,6 +7569,11 @@
           <t>Low profile handrail</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Corrimano a basso profilo.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7544,6 +7600,7 @@
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7570,6 +7627,7 @@
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7596,6 +7654,7 @@
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7622,6 +7681,7 @@
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7648,6 +7708,7 @@
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7674,6 +7735,7 @@
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7700,6 +7762,7 @@
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7726,6 +7789,7 @@
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7752,6 +7816,7 @@
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7782,6 +7847,11 @@
           <t>Colour: White</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Colore: bianco.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7808,6 +7878,7 @@
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7834,6 +7905,7 @@
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7860,6 +7932,7 @@
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7890,6 +7963,11 @@
           <t>Upgrade from 12 to 18 pax</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Upgrade da 12 a 18 persone.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7916,6 +7994,7 @@
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7942,6 +8021,7 @@
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7968,6 +8048,7 @@
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7994,6 +8075,7 @@
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -8020,6 +8102,7 @@
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -8046,6 +8129,7 @@
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8072,6 +8156,7 @@
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8098,6 +8183,7 @@
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8124,6 +8210,7 @@
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8150,6 +8237,7 @@
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8176,6 +8264,7 @@
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8202,6 +8291,7 @@
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8228,6 +8318,7 @@
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8254,6 +8345,7 @@
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8280,6 +8372,7 @@
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8306,6 +8399,7 @@
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8332,6 +8426,7 @@
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8358,6 +8453,7 @@
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8388,6 +8484,11 @@
           <t>Emergency position indicator radiobeacon (precision type), with hydrostatic, automatic release and activation, I.M.O. approved. Customer required to provide M.M.S.I. for activation. Device cannot operate without connection or activation. Includes onboard GPS sensor, category 1.       After delivery, system activation under Customer’s responsibility.</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Radioboa di localizzazione d'emergenza (tipo di precisione), con rilascio idrostatico automatico e attivazione, approvata I.M.O. Il cliente deve fornire il codice M.M.S.I. per l'attivazione. Il dispositivo non può funzionare senza collegamento o attivazione. Include sensore GPS a bordo, categoria 1. Dopo la consegna l'attivazione del sistema è responsabilità del cliente.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8418,6 +8519,11 @@
           <t>Bow thruster with proportional propellers included</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Include elica di prua con eliche proporzionali.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8444,6 +8550,7 @@
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8470,6 +8577,7 @@
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8496,6 +8604,7 @@
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8526,6 +8635,11 @@
           <t>To be selected only with OPT15208 - Proportional bow thruster upgrade</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Selezionabile solo insieme all'upgrade elica di prua proporzionale (OPT15208).</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8552,6 +8666,7 @@
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8582,6 +8697,11 @@
           <t>The upgrade includes: 4x 16” devo3 monitors on main bridge, 2x 12” evo3 monitors on flybridge</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>L'upgrade include: 4 monitor evo3 da 16” in plancia e 2 monitor evo3 da 12” sul flybridge.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8608,6 +8728,7 @@
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8634,6 +8755,7 @@
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8664,6 +8786,11 @@
           <t>Customer required to provide M.M.S.I. for activation. After delivery, system activation under Customer’s responsibility.</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Il cliente deve fornire il codice M.M.S.I. per l'attivazione. Dopo la consegna l'attivazione del sistema è responsabilità del cliente.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8690,6 +8817,7 @@
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8716,6 +8844,7 @@
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8746,6 +8875,11 @@
           <t>Requires joystick (OPT14747) with bow and stern thrusters, proportional propellers included</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Richiede il joystick (OPT14747) con eliche di prua e di poppa, eliche proporzionali incluse.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8772,6 +8906,7 @@
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8798,6 +8933,7 @@
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8824,6 +8960,7 @@
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8854,6 +8991,11 @@
           <t>Upgrade from std fixed 43”.</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Upgrade dal TV fisso standard da 43”.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8884,6 +9026,11 @@
           <t>Upgrade from std 50”.</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Upgrade dal TV standard da 50”.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8910,6 +9057,7 @@
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8936,6 +9084,7 @@
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8962,6 +9111,7 @@
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8992,6 +9142,11 @@
           <t>Additional in Master</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Aggiuntivo nella cabina armatoriale.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9018,6 +9173,7 @@
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9044,6 +9200,7 @@
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9070,6 +9227,7 @@
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9096,6 +9254,7 @@
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9126,6 +9285,11 @@
           <t>Additional wifi access point and external antenna for full yacht coverage. All electronic devices and cabins will be equipped with wired connections (switch hub POE 24 ports).</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Access point wifi aggiuntivo e antenna esterna per la copertura completa dello yacht. Tutti i dispositivi elettronici e le cabine avranno collegamenti cablati (switch hub POE a 24 porte).</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9156,6 +9320,11 @@
           <t>BOW AREA: No. 2 JL Audio SPEAKERS + FUSION MS400; FLYBRIDGE: No. 4 JL Audio SPEAKERS + 1 AMPLIFIER; COCKPIT: No. 4 JL Audio SPEAKERS + 2 AMPLIFIERS</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>PRUA: 2 altoparlanti JL Audio + FUSION MS400; FLYBRIDGE: 4 altoparlanti JL Audio + 1 amplificatore; POZZETTO: 4 altoparlanti JL Audio + 2 amplificatori.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9182,6 +9351,7 @@
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9212,6 +9382,11 @@
           <t>No. 1 antenna</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1 antenna.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9238,6 +9413,7 @@
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9264,6 +9440,7 @@
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9290,6 +9467,7 @@
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9316,6 +9494,7 @@
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9346,6 +9525,11 @@
           <t>Includes Racor filter, smoke separator and 2x22kW generators, upgrade from std 11 kW</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Include filtro Racor, separatore di fumi e 2 generatori da 22 kW, upgrade dallo standard da 11 kW.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9372,6 +9556,7 @@
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9398,6 +9583,7 @@
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9424,6 +9610,7 @@
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9450,6 +9637,7 @@
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9480,6 +9668,11 @@
           <t>OPT where applicable, as specified in the lighting design plan.</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Dove applicabile, come specificato nel progetto illuminotecnico.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9506,6 +9699,7 @@
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9532,6 +9726,7 @@
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9558,6 +9753,7 @@
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9584,6 +9780,7 @@
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9610,6 +9807,7 @@
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9640,6 +9838,11 @@
           <t>Includes lights for staircase to lowerdeck, strip lights under beds</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Include le luci della scala verso il ponte inferiore e le strisce luminose sotto i letti.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9666,6 +9869,7 @@
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9692,6 +9896,7 @@
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9718,6 +9923,7 @@
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9744,6 +9950,7 @@
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9770,6 +9977,7 @@
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9796,6 +10004,7 @@
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9822,6 +10031,7 @@
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9848,6 +10058,7 @@
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9874,6 +10085,7 @@
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9900,6 +10112,7 @@
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9926,6 +10139,7 @@
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9956,6 +10170,11 @@
           <t>Available for master head only</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Disponibile solo per il bagno armatoriale.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -9982,6 +10201,7 @@
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10008,6 +10228,7 @@
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10034,6 +10255,7 @@
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10060,6 +10282,7 @@
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10086,6 +10309,7 @@
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10116,6 +10340,11 @@
           <t>Refrigerator (50 l) on flybridge</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Frigorifero (50 l) sul flybridge.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10142,6 +10371,7 @@
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10172,6 +10402,11 @@
           <t>10-bottle capacity wine cellar</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Cantinetta con capacità di 10 bottiglie.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10202,6 +10437,11 @@
           <t>Includes 1x NG 6 and 1x NG 10.</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Include 1 NG 6 e 1 NG 10.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10228,6 +10468,7 @@
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10258,6 +10499,11 @@
           <t>Includes: 2 oil filters, 2 gas oil filters, 1 belt, 2 rotors, 2 anodes and 1 carrying case</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Include: 2 filtri olio, 2 filtri gasolio, 1 cinghia, 2 rotori, 2 anodi e 1 valigia.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10284,6 +10530,7 @@
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10310,6 +10557,7 @@
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10336,6 +10584,7 @@
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -10362,6 +10611,7 @@
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -10388,6 +10638,7 @@
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
